--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5189E49D-CEBF-404B-91AB-6D6874107A87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F01E47-5A3B-47C5-920D-A8455C271B6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,6 +47,26 @@
   </si>
   <si>
     <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>监控自己学习复习软件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R安装包为什么要指定type=binary类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R xmlRoot()命令不起作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R  could not find function "getHTMLLinks"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据如何更加准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -54,7 +74,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +87,14 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -102,15 +130,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,6 +435,7 @@
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -420,53 +463,85 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+    <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3">
+        <v>44064</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
+        <v>44064</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3">
+        <v>44064</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+    <row r="5" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3">
+        <v>44064</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+    <row r="6" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
+        <v>44064</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -629,7 +704,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{0861EE6B-F56C-4C71-A7AE-DBD42C11769C}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{6CBCC928-2911-4F1C-ABB0-ECEC505EA115}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{0D4355DE-EED1-4756-B539-5D0E0AA174D9}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{9D69DE50-49CD-46DC-8B4E-AD47ACAC0DB3}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{CE219D2D-95DE-42CC-B4C2-D869069D2EEE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F01E47-5A3B-47C5-920D-A8455C271B6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9180480A-5B64-4608-8141-2B1DC27A47BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -30,10 +30,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>问题计划结束日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>问题来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -67,6 +63,22 @@
   </si>
   <si>
     <t>数据如何更加准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linux centos 7.2 无法直接通过root用户登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同事</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -145,9 +157,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -430,277 +439,274 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D2" s="3">
         <v>44064</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="E2" s="3">
+        <v>44074</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>44064</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3">
         <v>44064</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3">
         <v>44064</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="3">
         <v>44064</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3">
+        <v>44074</v>
+      </c>
+      <c r="E7" s="3">
+        <v>44074</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -710,8 +716,9 @@
     <hyperlink ref="B4" r:id="rId3" xr:uid="{0D4355DE-EED1-4756-B539-5D0E0AA174D9}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{9D69DE50-49CD-46DC-8B4E-AD47ACAC0DB3}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{CE219D2D-95DE-42CC-B4C2-D869069D2EEE}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{53CAB822-FF6A-411C-B859-371E6CC05D67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9180480A-5B64-4608-8141-2B1DC27A47BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F1D77C-DB34-411C-A48C-71CA72446662}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F1D77C-DB34-411C-A48C-71CA72446662}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D37EE5-10CF-418A-BC65-33F8C7CA34AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D37EE5-10CF-418A-BC65-33F8C7CA34AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448238DC-27D5-4D41-8631-4B24CE072287}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,6 +79,14 @@
   </si>
   <si>
     <t>同事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greenplum not free disk and gprecoverseg failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gp的表路径和各个数据节点的表路径如何获取并且得到</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,21 +580,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+    <row r="8" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3">
+        <v>44086</v>
+      </c>
+      <c r="E8" s="3">
+        <v>44085</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3">
+        <v>44086</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
@@ -717,8 +745,9 @@
     <hyperlink ref="B5" r:id="rId4" xr:uid="{9D69DE50-49CD-46DC-8B4E-AD47ACAC0DB3}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{CE219D2D-95DE-42CC-B4C2-D869069D2EEE}"/>
     <hyperlink ref="B7" r:id="rId6" xr:uid="{53CAB822-FF6A-411C-B859-371E6CC05D67}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{3719560C-5D9C-4FB6-A7A7-9FEF1A40C340}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448238DC-27D5-4D41-8631-4B24CE072287}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C155A78-4D41-46EB-B128-65234F5DB4E2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,6 +87,14 @@
   </si>
   <si>
     <t>gp的表路径和各个数据节点的表路径如何获取并且得到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linux install clamav杀毒软件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -607,22 +615,34 @@
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="D9" s="3">
         <v>44086</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3">
+        <v>44089</v>
+      </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+    <row r="10" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3">
+        <v>44088</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -746,8 +766,10 @@
     <hyperlink ref="B6" r:id="rId5" xr:uid="{CE219D2D-95DE-42CC-B4C2-D869069D2EEE}"/>
     <hyperlink ref="B7" r:id="rId6" xr:uid="{53CAB822-FF6A-411C-B859-371E6CC05D67}"/>
     <hyperlink ref="B8" r:id="rId7" xr:uid="{3719560C-5D9C-4FB6-A7A7-9FEF1A40C340}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{61524DF5-3E0E-40A9-AF54-A3AB4B90E1D0}"/>
+    <hyperlink ref="B9" r:id="rId9" xr:uid="{75BA8FC0-D6C8-4130-91EB-3736A5CCEB61}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C155A78-4D41-46EB-B128-65234F5DB4E2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35461EAE-175C-4591-A190-61C838D6F209}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何能够在maxcomputer上传python函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将md文件后缀名不是01的修改名字按照从大到小来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算文档之间的重复率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,29 +656,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+    <row r="11" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3">
+        <v>44099</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3">
+        <v>44099</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3">
+        <v>44099</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -768,8 +804,9 @@
     <hyperlink ref="B8" r:id="rId7" xr:uid="{3719560C-5D9C-4FB6-A7A7-9FEF1A40C340}"/>
     <hyperlink ref="B10" r:id="rId8" xr:uid="{61524DF5-3E0E-40A9-AF54-A3AB4B90E1D0}"/>
     <hyperlink ref="B9" r:id="rId9" xr:uid="{75BA8FC0-D6C8-4130-91EB-3736A5CCEB61}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{6A9E79DB-B4E9-4B43-812D-31F9E87BECDF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35461EAE-175C-4591-A190-61C838D6F209}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8726E7B-9CEB-4A2C-BE1D-B8B64BFE4FEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -805,8 +805,10 @@
     <hyperlink ref="B10" r:id="rId8" xr:uid="{61524DF5-3E0E-40A9-AF54-A3AB4B90E1D0}"/>
     <hyperlink ref="B9" r:id="rId9" xr:uid="{75BA8FC0-D6C8-4130-91EB-3736A5CCEB61}"/>
     <hyperlink ref="B11" r:id="rId10" xr:uid="{6A9E79DB-B4E9-4B43-812D-31F9E87BECDF}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{6F776195-F6EA-4E79-8367-47D739BCFE95}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{303B92E3-B157-4996-91BA-49212F149961}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8726E7B-9CEB-4A2C-BE1D-B8B64BFE4FEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB6D227-4E3F-43A7-A19C-FFA4F16B16F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,6 +107,10 @@
   </si>
   <si>
     <t>计算文档之间的重复率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将照片重命名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +655,9 @@
       <c r="D10" s="3">
         <v>44088</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3">
+        <v>44094</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>14</v>
       </c>
@@ -667,7 +673,9 @@
       <c r="D11" s="3">
         <v>44099</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3">
+        <v>44104</v>
+      </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
       </c>
@@ -683,7 +691,9 @@
       <c r="D12" s="3">
         <v>44099</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="3">
+        <v>44104</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
       </c>
@@ -704,13 +714,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+    <row r="14" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3">
+        <v>44108</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -807,8 +825,9 @@
     <hyperlink ref="B11" r:id="rId10" xr:uid="{6A9E79DB-B4E9-4B43-812D-31F9E87BECDF}"/>
     <hyperlink ref="B12" r:id="rId11" xr:uid="{6F776195-F6EA-4E79-8367-47D739BCFE95}"/>
     <hyperlink ref="B13" r:id="rId12" xr:uid="{303B92E3-B157-4996-91BA-49212F149961}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{0847409C-E7EF-4064-8E29-00F305FD69F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB6D227-4E3F-43A7-A19C-FFA4F16B16F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95552A-A765-4239-9D09-60F9114850DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95552A-A765-4239-9D09-60F9114850DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C97BF9-7380-4EE5-88FB-3F02FD7ECDD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,6 +113,9 @@
   <si>
     <t>将照片重命名</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/reading-excel-file-using-python/</t>
   </si>
 </sst>
 </file>
@@ -178,7 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -190,6 +194,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -830,4 +835,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF9B8CB-BF46-45A1-ADF4-39A4E445D7BB}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{0A79D699-7431-4527-9385-C3B5F157721D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C97BF9-7380-4EE5-88FB-3F02FD7ECDD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD26AA7-2221-4ECD-8C7C-E07DC6E8E82F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,6 +116,10 @@
   </si>
   <si>
     <t>https://www.geeksforgeeks.org/reading-excel-file-using-python/</t>
+  </si>
+  <si>
+    <t>ModuleNotFoundError: No module named 'pygal.i18n'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -735,13 +739,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+    <row r="15" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3">
+        <v>44111</v>
+      </c>
+      <c r="E15" s="3">
+        <v>44111</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -831,9 +845,10 @@
     <hyperlink ref="B12" r:id="rId11" xr:uid="{6F776195-F6EA-4E79-8367-47D739BCFE95}"/>
     <hyperlink ref="B13" r:id="rId12" xr:uid="{303B92E3-B157-4996-91BA-49212F149961}"/>
     <hyperlink ref="B14" r:id="rId13" xr:uid="{0847409C-E7EF-4064-8E29-00F305FD69F8}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{CD3BC8E4-EADD-4E64-8B82-207480AFCDD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD26AA7-2221-4ECD-8C7C-E07DC6E8E82F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BA6C1B-B8B5-475D-9390-3F98616570EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -119,6 +119,26 @@
   </si>
   <si>
     <t>ModuleNotFoundError: No module named 'pygal.i18n'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>粘贴网上文档，同时将照片的链接粘贴下来，将照片下载到本地并替换到文档中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>照片链接换行如何下载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>urllib2 无法在python获取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>python pandas？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,7 +505,7 @@
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -660,7 +680,9 @@
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D10" s="3">
         <v>44088</v>
       </c>
@@ -678,7 +700,9 @@
       <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D11" s="3">
         <v>44099</v>
       </c>
@@ -696,7 +720,9 @@
       <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D12" s="3">
         <v>44099</v>
       </c>
@@ -730,11 +756,15 @@
       <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="D14" s="3">
         <v>44108</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="3">
+        <v>44115</v>
+      </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
       </c>
@@ -746,7 +776,9 @@
       <c r="B15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D15" s="3">
         <v>44111</v>
       </c>
@@ -757,37 +789,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+    <row r="16" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="3">
+        <v>44115</v>
+      </c>
+      <c r="E16" s="3">
+        <v>44115</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3">
+        <v>44115</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="3">
+        <v>44115</v>
+      </c>
+      <c r="E18" s="3">
+        <v>44115</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="3">
+        <v>44115</v>
+      </c>
+      <c r="E19" s="3">
+        <v>44115</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -846,9 +922,13 @@
     <hyperlink ref="B13" r:id="rId12" xr:uid="{303B92E3-B157-4996-91BA-49212F149961}"/>
     <hyperlink ref="B14" r:id="rId13" xr:uid="{0847409C-E7EF-4064-8E29-00F305FD69F8}"/>
     <hyperlink ref="B15" r:id="rId14" xr:uid="{CD3BC8E4-EADD-4E64-8B82-207480AFCDD0}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{FA2D478F-BEEE-41FD-9EB8-93122037BBC7}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{4E8F33A4-D8B9-4B0C-8A6C-4B30CDC8771A}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{4D400480-3762-41D1-9A10-4179A6E92263}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{2AD023B8-6179-4B2A-8102-9A2C78B81F6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
 

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BA6C1B-B8B5-475D-9390-3F98616570EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B25C985-83B7-45E2-9718-D7C08643FB87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="节制" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -206,7 +206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -219,6 +219,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -866,7 +869,9 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B25C985-83B7-45E2-9718-D7C08643FB87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A259984-5721-4D77-8EF6-7961850FC269}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,6 +139,10 @@
   </si>
   <si>
     <t>python pandas？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在geany中创建py:SyntaxError: (unicode error) 'utf-8' codec can't decode byte 0xb1 in position 0: invalid start byte</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -206,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -219,9 +223,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -868,18 +869,30 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="20" spans="1:6" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="3">
+        <v>44116</v>
+      </c>
+      <c r="E20" s="3">
+        <v>44116</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -931,9 +944,10 @@
     <hyperlink ref="B17" r:id="rId16" xr:uid="{4E8F33A4-D8B9-4B0C-8A6C-4B30CDC8771A}"/>
     <hyperlink ref="B18" r:id="rId17" xr:uid="{4D400480-3762-41D1-9A10-4179A6E92263}"/>
     <hyperlink ref="B19" r:id="rId18" xr:uid="{2AD023B8-6179-4B2A-8102-9A2C78B81F6F}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{3F04B380-9D12-4480-A3A1-58CE9F3F80A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>
 

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A259984-5721-4D77-8EF6-7961850FC269}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECD79CF-6750-4545-8A13-62CC3DEFB603}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="节制" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20363"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20367"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECD79CF-6750-4545-8A13-62CC3DEFB603}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CD3393-7AFE-4F51-AB8E-827800E65904}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>在geany中创建py:SyntaxError: (unicode error) 'utf-8' codec can't decode byte 0xb1 in position 0: invalid start byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ValueError: A string literal cannot contain NUL (0x00) characters.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>python:开发一个可以输入参数让其下载excel网站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xlwt.ExcelMagic has no attribute 'std_func_by_name'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -889,31 +901,57 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="3">
+        <v>44137</v>
+      </c>
+      <c r="E21" s="3">
+        <v>44137</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3">
+        <v>44137</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3">
+        <v>44138</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -945,9 +983,12 @@
     <hyperlink ref="B18" r:id="rId17" xr:uid="{4D400480-3762-41D1-9A10-4179A6E92263}"/>
     <hyperlink ref="B19" r:id="rId18" xr:uid="{2AD023B8-6179-4B2A-8102-9A2C78B81F6F}"/>
     <hyperlink ref="B20" r:id="rId19" xr:uid="{3F04B380-9D12-4480-A3A1-58CE9F3F80A4}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{013A49DB-2EF7-452E-BDC3-A0ED6DEE1941}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{3FE4BF83-FEB8-4C4C-9656-B922F2ACB8B9}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{0DDE6A94-F040-4263-B8C7-9C5A89C2BFDE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
 </worksheet>
 </file>
 

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20367"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CD3393-7AFE-4F51-AB8E-827800E65904}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8E11AD-50BC-48E1-8B39-FF1DD3A0B326}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,6 +155,10 @@
   </si>
   <si>
     <t>xlwt.ExcelMagic has no attribute 'std_func_by_name'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Http协议是什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -222,9 +226,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -526,440 +529,448 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2">
         <v>44064</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>44074</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
+      <c r="C3" s="1"/>
+      <c r="D3" s="2">
         <v>44064</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
+      <c r="C4" s="1"/>
+      <c r="D4" s="2">
         <v>44064</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="C5" s="1"/>
+      <c r="D5" s="2">
         <v>44064</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
+      <c r="C6" s="1"/>
+      <c r="D6" s="2">
         <v>44064</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2">
         <v>44074</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>44074</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2">
         <v>44086</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>44085</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>44086</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>44089</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2">
         <v>44088</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>44094</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2">
         <v>44099</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>44104</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="2">
         <v>44099</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>44104</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="3">
+      <c r="C13" s="1"/>
+      <c r="D13" s="2">
         <v>44099</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>44108</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>44115</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="C15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2">
         <v>44111</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <v>44111</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2">
         <v>44115</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>44115</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="3">
+      <c r="C17" s="1"/>
+      <c r="D17" s="2">
         <v>44115</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2">
         <v>44115</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>44115</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2">
         <v>44115</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>44115</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2">
         <v>44116</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>44116</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="C21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2">
         <v>44137</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>44137</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3">
+      <c r="C22" s="1"/>
+      <c r="D22" s="2">
         <v>44137</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="2"/>
+      <c r="F22" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3">
+      <c r="C23" s="1"/>
+      <c r="D23" s="2">
         <v>44138</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="D24" s="2">
+        <v>44150</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -998,7 +1009,7 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
     </row>

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20367"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20368"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8E11AD-50BC-48E1-8B39-FF1DD3A0B326}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA24A0B-BB51-4175-B443-25454CD7F576}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,6 +159,10 @@
   </si>
   <si>
     <t>Http协议是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kettle 8.x kafka consumer 如何配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -969,6 +973,22 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="2">
+        <v>44165</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -997,9 +1017,10 @@
     <hyperlink ref="B21" r:id="rId20" xr:uid="{013A49DB-2EF7-452E-BDC3-A0ED6DEE1941}"/>
     <hyperlink ref="B22" r:id="rId21" xr:uid="{3FE4BF83-FEB8-4C4C-9656-B922F2ACB8B9}"/>
     <hyperlink ref="B23" r:id="rId22" xr:uid="{0DDE6A94-F040-4263-B8C7-9C5A89C2BFDE}"/>
+    <hyperlink ref="B25" r:id="rId23" xr:uid="{61A1D507-14B2-4A81-B18B-99BA70A74423}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
 

--- a/question/question.xlsx
+++ b/question/question.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20368"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA24A0B-BB51-4175-B443-25454CD7F576}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A67185-7D90-42AC-B70C-3C78AD3C1EEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="节制" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
   <si>
     <t>问题日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>kettle 8.x kafka consumer 如何配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>python oracle DPI-1047</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -523,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -989,6 +993,22 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="2">
+        <v>44172</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1018,9 +1038,10 @@
     <hyperlink ref="B22" r:id="rId21" xr:uid="{3FE4BF83-FEB8-4C4C-9656-B922F2ACB8B9}"/>
     <hyperlink ref="B23" r:id="rId22" xr:uid="{0DDE6A94-F040-4263-B8C7-9C5A89C2BFDE}"/>
     <hyperlink ref="B25" r:id="rId23" xr:uid="{61A1D507-14B2-4A81-B18B-99BA70A74423}"/>
+    <hyperlink ref="B26" r:id="rId24" xr:uid="{16725526-B565-4905-8599-8680E5701EB4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
 
